--- a/reports/集团总公司_利润表_2026-04.xlsx
+++ b/reports/集团总公司_利润表_2026-04.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>225534259</v>
+        <v>245839348</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>171398892</v>
+        <v>186653905</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>620926969</v>
+        <v>675757064</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>699233</v>
+        <v>907272</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2632546</v>
+        <v>3416795</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>606789</v>
+        <v>792424</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2284172</v>
+        <v>2988498</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>516089</v>
+        <v>667864</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1937303</v>
+        <v>2520903</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>474154</v>
+        <v>615754</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1781800</v>
+        <v>2324672</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>256889</v>
+        <v>338473</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>967689</v>
+        <v>1277120</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>206007</v>
+        <v>266715</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>774558</v>
+        <v>1005292</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>222775098</v>
+        <v>242250846</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>168639731</v>
+        <v>183065403</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>87010860</v>
+        <v>95005762</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>302511167</v>
+        <v>332561982</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1597874</v>
+        <v>2839109</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>6003966</v>
+        <v>10639269</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1444427</v>
+        <v>2067135</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5423995</v>
+        <v>7741927</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>76869497</v>
+        <v>81838349</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>290144643</v>
+        <v>306331772</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1645275</v>
+        <v>2069276</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>6194093</v>
+        <v>7761693</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>723419</v>
+        <v>1033032</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2712979</v>
+        <v>3882292</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2575478</v>
+        <v>3094964</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>9682585</v>
+        <v>11654092</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1129936</v>
+        <v>1545387</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4257507</v>
+        <v>5823306</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>53959605</v>
+        <v>53574214</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>202618947</v>
+        <v>202382332</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>175762</v>
+        <v>174456</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>688665</v>
+        <v>700566</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3262304</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>12313712</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2174469</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8200684</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>163039474</v>
+        <v>184769465</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>130765398</v>
+        <v>138203941</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>102866889</v>
+        <v>110143212</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>387621082</v>
+        <v>413934109</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27898509</v>
+        <v>28060729</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>104938349</v>
+        <v>104976972</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5472885</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>20498583</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1753332</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6566166</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1096379</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4108224</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1315342</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4934465</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>985590</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3703208</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>656099</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2469372</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>545800</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2057364</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3050559</v>
+        <v>3030475</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>11434805</v>
+        <v>11438051</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1432306</v>
+        <v>1428078</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5383763</v>
+        <v>5393726</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3689466</v>
+        <v>3693267</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>13926544</v>
+        <v>13913278</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>24021501</v>
+        <v>23928709</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>90253384</v>
+        <v>90015261</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>361366</v>
+        <v>2935594</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1393360</v>
+        <v>11004581</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1151184</v>
+        <v>1152052</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4526357</v>
+        <v>4603107</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1191211</v>
+        <v>1101140</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4676766</v>
+        <v>4399788</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>123931</v>
+        <v>123704</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>482288</v>
+        <v>493287</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>492651</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1962570</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>958955</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3591383</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>328917</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1311083</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>246605</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>984234</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>410593</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1641455</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1366569</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5144510</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>218269</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>875483</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163426</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>656212</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>272020</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1092687</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>190278</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>764070</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>135914</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>545209</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>108812</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>435822</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81718</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>326725</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>59735624</v>
+        <v>60843961</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>64516298</v>
+        <v>65279915</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>547485</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2050377</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>137007</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>545782</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>216857</v>
+        <v>217205</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>845828</v>
+        <v>865921</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>59518767</v>
+        <v>61174241</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7289274</v>
+        <v>7334132</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>28540874</v>
+        <v>29320215</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>52229493</v>
+        <v>53840109</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>52229493</v>
+        <v>53840109</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>52229493</v>
+        <v>53840109</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>52229493</v>
+        <v>53840109</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>52229493</v>
+        <v>53840109</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
